--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2288,6 +2288,127 @@
       <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129189112</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136759860</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99346</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tandsjöborg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>485902</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6845921</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136759860</t>
         </is>
       </c>
     </row>
@@ -2308,6 +2429,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 48335-2025 artfynd.xlsx
+++ b/artfynd/A 48335-2025 artfynd.xlsx
@@ -2296,7 +2296,7 @@
         <v>136759860</v>
       </c>
       <c r="B17" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
